--- a/artfynd/A 31007-2026 artfynd.xlsx
+++ b/artfynd/A 31007-2026 artfynd.xlsx
@@ -22933,7 +22933,7 @@
         <v>136156620</v>
       </c>
       <c r="B196" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
